--- a/docs/data/raw/2026-05-09_ST.xlsx
+++ b/docs/data/raw/2026-05-09_ST.xlsx
@@ -4786,7 +4786,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>E C W Wong (-3)</t>
+          <t>K Teetan</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -23370,7 +23370,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>E C W Wong (-3)</t>
+          <t>K Teetan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
